--- a/output/timetable_all_departments_even.xlsx
+++ b/output/timetable_all_departments_even.xlsx
@@ -78,12 +78,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
@@ -92,6 +86,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
         <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -182,15 +182,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -807,7 +807,145 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>CS502
+LEC
+Room: 102
+Dr. NormalTest</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="n"/>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>CS502
+LEC
+Room: 102
+Dr. NormalTest</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>CS502
+TUT
+Room: 102
+Dr. NormalTest</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>CS501
 LEC
@@ -815,158 +953,27 @@
 Dr. BlockTest</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="inlineStr"/>
-      <c r="H2" s="11" t="inlineStr"/>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr"/>
-      <c r="K2" s="11" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr"/>
-      <c r="N2" s="11" t="inlineStr"/>
-      <c r="O2" s="11" t="inlineStr"/>
-      <c r="P2" s="11" t="inlineStr"/>
-      <c r="Q2" s="13" t="inlineStr">
-        <is>
-          <t>CS502
-LEC
-Room: 101
-Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="11" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr"/>
-      <c r="D3" s="11" t="inlineStr"/>
-      <c r="E3" s="11" t="inlineStr"/>
-      <c r="F3" s="11" t="inlineStr"/>
-      <c r="G3" s="11" t="inlineStr"/>
-      <c r="H3" s="11" t="inlineStr"/>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
-      <c r="K3" s="11" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr"/>
-      <c r="N3" s="11" t="inlineStr"/>
-      <c r="O3" s="11" t="inlineStr"/>
-      <c r="P3" s="11" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
-        <is>
-          <t>CS502
-LEC
-Room: 101
-Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="R3" s="9" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="11" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr"/>
-      <c r="G4" s="11" t="inlineStr"/>
-      <c r="H4" s="11" t="inlineStr"/>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr"/>
-      <c r="K4" s="11" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr"/>
-      <c r="N4" s="11" t="inlineStr"/>
-      <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="11" t="inlineStr"/>
-      <c r="Q4" s="11" t="inlineStr"/>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr"/>
-      <c r="T4" s="11" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr"/>
-      <c r="D5" s="11" t="inlineStr"/>
-      <c r="E5" s="11" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
-      <c r="H5" s="11" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr"/>
-      <c r="N5" s="11" t="inlineStr"/>
-      <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="11" t="inlineStr"/>
-      <c r="Q5" s="11" t="inlineStr"/>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr"/>
-      <c r="T5" s="11" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -984,35 +991,28 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>CS502
-TUT
-Room: 102
-Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="11" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
-      <c r="Q6" s="11" t="inlineStr"/>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1110,16 +1110,15 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
+  <mergeCells count="3">
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1276,7 +1275,145 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>CS502
+LEC
+Room: 102
+Dr. NormalTest</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="n"/>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>CS502
+LEC
+Room: 102
+Dr. NormalTest</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>CS502
+TUT
+Room: 102
+Dr. NormalTest</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>CS501
 LEC
@@ -1284,158 +1421,27 @@
 Dr. BlockTest</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="inlineStr"/>
-      <c r="H2" s="11" t="inlineStr"/>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr"/>
-      <c r="K2" s="11" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr"/>
-      <c r="N2" s="11" t="inlineStr"/>
-      <c r="O2" s="11" t="inlineStr"/>
-      <c r="P2" s="11" t="inlineStr"/>
-      <c r="Q2" s="13" t="inlineStr">
-        <is>
-          <t>CS502
-LEC
-Room: 101
-Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="11" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr"/>
-      <c r="D3" s="11" t="inlineStr"/>
-      <c r="E3" s="11" t="inlineStr"/>
-      <c r="F3" s="11" t="inlineStr"/>
-      <c r="G3" s="11" t="inlineStr"/>
-      <c r="H3" s="11" t="inlineStr"/>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
-      <c r="K3" s="11" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr"/>
-      <c r="N3" s="11" t="inlineStr"/>
-      <c r="O3" s="11" t="inlineStr"/>
-      <c r="P3" s="11" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
-        <is>
-          <t>CS502
-LEC
-Room: 101
-Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="R3" s="9" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="11" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr"/>
-      <c r="G4" s="11" t="inlineStr"/>
-      <c r="H4" s="11" t="inlineStr"/>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr"/>
-      <c r="K4" s="11" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr"/>
-      <c r="N4" s="11" t="inlineStr"/>
-      <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="11" t="inlineStr"/>
-      <c r="Q4" s="11" t="inlineStr"/>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr"/>
-      <c r="T4" s="11" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr"/>
-      <c r="D5" s="11" t="inlineStr"/>
-      <c r="E5" s="11" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
-      <c r="H5" s="11" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr"/>
-      <c r="N5" s="11" t="inlineStr"/>
-      <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="11" t="inlineStr"/>
-      <c r="Q5" s="11" t="inlineStr"/>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr"/>
-      <c r="T5" s="11" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1453,35 +1459,28 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>CS502
-TUT
-Room: 102
-Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="11" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
-      <c r="Q6" s="11" t="inlineStr"/>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1579,16 +1578,15 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
+  <mergeCells count="3">
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1600,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1655,19 +1653,19 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. BlockTest</t>
+          <t>Dr. NormalTest</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1677,7 +1675,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS501</t>
+          <t>CS502</t>
         </is>
       </c>
     </row>
@@ -1688,13 +1686,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1703,7 +1701,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1724,17 +1722,17 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>17</v>
-      </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. NormalTest</t>
+          <t>Dr. BlockTest</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1749,24 +1747,24 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS502</t>
+          <t>CS501</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CSE_4_A</t>
+          <t>CSE_4_B</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1780,7 +1778,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1796,22 +1794,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. BlockTest</t>
+          <t>Dr. NormalTest</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1821,7 +1819,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS501</t>
+          <t>CS502</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1830,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. NormalTest</t>
+          <t>Dr. BlockTest</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1857,79 +1855,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS502</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>17</v>
-      </c>
-      <c r="D8" t="n">
-        <v>19</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>CS502</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Dr. NormalTest</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CS502</t>
+          <t>CS501</t>
         </is>
       </c>
     </row>
